--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 05/02. Trả bảo hành/TBH_AnhTuanBG_190526.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 05/02. Trả bảo hành/TBH_AnhTuanBG_190526.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 05\02. Trả bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EDED7E7-A992-4F0B-990F-687EB918D494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F231C1A1-0FAF-4AFD-9540-A5B0974EB947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="P.TraBaoHanh" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">P.TraBaoHanh!$A$1:$I$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">P.TraBaoHanh!$A$1:$I$31</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="56">
   <si>
     <t xml:space="preserve">STT </t>
   </si>
@@ -112,6 +112,87 @@
   <si>
     <t>Test lại chức 
 năng của thiết bị</t>
+  </si>
+  <si>
+    <t>005185070142792</t>
+  </si>
+  <si>
+    <t>005185070148468</t>
+  </si>
+  <si>
+    <t>005185070139178</t>
+  </si>
+  <si>
+    <t>005185070142610</t>
+  </si>
+  <si>
+    <t>005581052581338</t>
+  </si>
+  <si>
+    <t>862205051204792</t>
+  </si>
+  <si>
+    <t>862205051221622</t>
+  </si>
+  <si>
+    <t>005694061435520</t>
+  </si>
+  <si>
+    <t>007785070718948</t>
+  </si>
+  <si>
+    <t>Còn BH</t>
+  </si>
+  <si>
+    <t>Mất giao tiếp</t>
+  </si>
+  <si>
+    <t>Nạp lại FW, test lại thiết bị</t>
+  </si>
+  <si>
+    <t>SIM lỗi, hết hạn DV</t>
+  </si>
+  <si>
+    <t>Lỗi còi, chốt SIM chậm</t>
+  </si>
+  <si>
+    <t>Thay còi, nạp lại FW module SIM</t>
+  </si>
+  <si>
+    <t>Không chốt SIM</t>
+  </si>
+  <si>
+    <t>Nâng cấp FW module SIM</t>
+  </si>
+  <si>
+    <t>Chốt SIM chậm</t>
+  </si>
+  <si>
+    <t>Nạp lại FW module SIM</t>
+  </si>
+  <si>
+    <t>IC chuyển động không hoạt động</t>
+  </si>
+  <si>
+    <t>Nạp lại FW</t>
+  </si>
+  <si>
+    <t>Nạp lại FW test lại thiết bị</t>
+  </si>
+  <si>
+    <t>TG102LE-4G</t>
+  </si>
+  <si>
+    <t>SIM</t>
+  </si>
+  <si>
+    <t>Hết BH</t>
+  </si>
+  <si>
+    <t>eSIM: 01388614668</t>
+  </si>
+  <si>
+    <t>eSIM: 0842462610</t>
   </si>
 </sst>
 </file>
@@ -121,7 +202,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="@*."/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -227,12 +308,6 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -372,7 +447,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -452,15 +527,6 @@
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -470,10 +536,25 @@
     <xf numFmtId="3" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -509,25 +590,22 @@
     <xf numFmtId="49" fontId="12" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -893,7 +971,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="5" customWidth="1"/>
@@ -902,8 +980,8 @@
     <col min="4" max="4" width="11.28515625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.5703125" style="1" customWidth="1"/>
     <col min="6" max="6" width="19" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.28515625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="19" style="2" customWidth="1"/>
+    <col min="7" max="7" width="24.28515625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" style="2" customWidth="1"/>
     <col min="9" max="9" width="14" style="4" customWidth="1"/>
     <col min="10" max="12" width="9.140625" style="1"/>
     <col min="13" max="13" width="0" style="1" hidden="1" customWidth="1"/>
@@ -911,77 +989,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="41"/>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="42" t="s">
+      <c r="A1" s="43"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
     </row>
     <row r="2" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="41"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="43" t="s">
+      <c r="A2" s="43"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="45"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="47"/>
     </row>
     <row r="3" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="41"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="46" t="s">
+      <c r="A3" s="43"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="48"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="50"/>
     </row>
     <row r="4" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="41"/>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="49" t="s">
+      <c r="A4" s="43"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="51"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="53"/>
     </row>
     <row r="5" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="37"/>
+      <c r="I5" s="37"/>
     </row>
     <row r="6" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="55" t="s">
+      <c r="A6" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
       <c r="E6" s="22"/>
       <c r="F6" s="20"/>
       <c r="G6" s="20"/>
@@ -991,12 +1069,12 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="55" t="s">
+      <c r="A7" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
       <c r="E7" s="22"/>
       <c r="F7" s="21"/>
       <c r="G7" s="21"/>
@@ -1004,12 +1082,12 @@
       <c r="I7" s="21"/>
     </row>
     <row r="8" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="55" t="s">
+      <c r="A8" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="55"/>
-      <c r="C8" s="55"/>
-      <c r="D8" s="55"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
       <c r="E8" s="22"/>
       <c r="F8" s="20"/>
       <c r="G8" s="20"/>
@@ -1017,12 +1095,12 @@
       <c r="I8" s="20"/>
     </row>
     <row r="9" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="55" t="s">
+      <c r="A9" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="55"/>
-      <c r="C9" s="55"/>
-      <c r="D9" s="55"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
       <c r="E9" s="22"/>
       <c r="F9" s="20"/>
       <c r="G9" s="20"/>
@@ -1030,222 +1108,446 @@
       <c r="I9" s="20"/>
     </row>
     <row r="10" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="36" t="s">
+      <c r="A10" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="36" t="s">
+      <c r="B10" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="37" t="s">
+      <c r="C10" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="37" t="s">
+      <c r="D10" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="37" t="s">
+      <c r="E10" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="F10" s="37" t="s">
+      <c r="F10" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="G10" s="37" t="s">
+      <c r="G10" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="37" t="s">
+      <c r="H10" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="38" t="s">
+      <c r="I10" s="35" t="s">
         <v>18</v>
       </c>
       <c r="J10" s="7"/>
     </row>
-    <row r="11" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="33">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="54">
         <v>1</v>
       </c>
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="54" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="56"/>
+      <c r="E11" s="56" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="56"/>
+      <c r="G11" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" s="56" t="s">
+        <v>40</v>
+      </c>
+      <c r="I11" s="57"/>
+      <c r="J11" s="7"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="54">
+        <v>2</v>
+      </c>
+      <c r="B12" s="54" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="55" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="56" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="56" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="H12" s="56" t="s">
+        <v>40</v>
+      </c>
+      <c r="I12" s="57"/>
+      <c r="J12" s="7"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="54">
+        <v>3</v>
+      </c>
+      <c r="B13" s="54" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="55" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="56"/>
+      <c r="G13" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="H13" s="56" t="s">
+        <v>40</v>
+      </c>
+      <c r="I13" s="57"/>
+      <c r="J13" s="7"/>
+    </row>
+    <row r="14" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="54">
+        <v>4</v>
+      </c>
+      <c r="B14" s="54" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="55" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="56"/>
+      <c r="G14" s="56" t="s">
+        <v>42</v>
+      </c>
+      <c r="H14" s="56" t="s">
+        <v>43</v>
+      </c>
+      <c r="I14" s="57"/>
+      <c r="J14" s="7"/>
+    </row>
+    <row r="15" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="54">
+        <v>5</v>
+      </c>
+      <c r="B15" s="54" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="55" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="56"/>
+      <c r="G15" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="H15" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="I15" s="57"/>
+      <c r="J15" s="7"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="54">
+        <v>6</v>
+      </c>
+      <c r="B16" s="54" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="56"/>
+      <c r="G16" s="56" t="s">
+        <v>46</v>
+      </c>
+      <c r="H16" s="56" t="s">
+        <v>47</v>
+      </c>
+      <c r="I16" s="57"/>
+      <c r="J16" s="7"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="54">
+        <v>7</v>
+      </c>
+      <c r="B17" s="54" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="55" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="56"/>
+      <c r="G17" s="56" t="s">
+        <v>46</v>
+      </c>
+      <c r="H17" s="56" t="s">
+        <v>47</v>
+      </c>
+      <c r="I17" s="57"/>
+      <c r="J17" s="7"/>
+    </row>
+    <row r="18" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="54">
+        <v>8</v>
+      </c>
+      <c r="B18" s="54" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="55" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" s="56" t="s">
+        <v>54</v>
+      </c>
+      <c r="G18" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="H18" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="I18" s="57"/>
+      <c r="J18" s="7"/>
+    </row>
+    <row r="19" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="54">
+        <v>9</v>
+      </c>
+      <c r="B19" s="54" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="55" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" s="56" t="s">
+        <v>55</v>
+      </c>
+      <c r="G19" s="56" t="s">
+        <v>27</v>
+      </c>
+      <c r="H19" s="56" t="s">
+        <v>50</v>
+      </c>
+      <c r="I19" s="57"/>
+      <c r="J19" s="7"/>
+    </row>
+    <row r="20" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="54">
+        <v>10</v>
+      </c>
+      <c r="B20" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="40" t="s">
+      <c r="C20" s="59" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="34" t="s">
+      <c r="D20" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="34" t="s">
+      <c r="E20" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="39"/>
-      <c r="G11" s="34" t="s">
+      <c r="F20" s="58"/>
+      <c r="G20" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="H11" s="34" t="s">
+      <c r="H20" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="I11" s="35"/>
-      <c r="J11" s="7"/>
-    </row>
-    <row r="12" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="24"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="7"/>
-    </row>
-    <row r="13" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="11"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="27"/>
-    </row>
-    <row r="14" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="56" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="56"/>
-      <c r="C14" s="56"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="58" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="58"/>
-      <c r="I14" s="58"/>
-    </row>
-    <row r="15" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="57" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="57"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="57" t="s">
-        <v>13</v>
-      </c>
-      <c r="H15" s="57"/>
-      <c r="I15" s="57"/>
-    </row>
-    <row r="16" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="28"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-    </row>
-    <row r="17" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="29"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="9"/>
-    </row>
-    <row r="18" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="29"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="9"/>
-    </row>
-    <row r="19" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="29"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="9"/>
-    </row>
-    <row r="20" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="28"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="17"/>
-    </row>
-    <row r="21" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="56" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21" s="56"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="56"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="56" t="s">
-        <v>5</v>
-      </c>
-      <c r="H21" s="56"/>
-      <c r="I21" s="56"/>
-    </row>
-    <row r="22" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I20" s="57"/>
+      <c r="J20" s="7"/>
+    </row>
+    <row r="21" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="24"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="7"/>
+    </row>
+    <row r="22" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11"/>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
       <c r="E22" s="12"/>
       <c r="F22" s="12"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="19"/>
-    </row>
-    <row r="24" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B24" s="54"/>
-      <c r="C24" s="54"/>
-    </row>
-    <row r="63" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="27"/>
+    </row>
+    <row r="23" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="40"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
+    </row>
+    <row r="24" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="41"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="41"/>
+      <c r="I24" s="41"/>
+    </row>
+    <row r="25" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="28"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+    </row>
+    <row r="26" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="29"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="9"/>
+    </row>
+    <row r="27" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="29"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="9"/>
+    </row>
+    <row r="28" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="29"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="9"/>
+    </row>
+    <row r="29" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="28"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="16"/>
+      <c r="I29" s="17"/>
+    </row>
+    <row r="30" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" s="40"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="H30" s="40"/>
+      <c r="I30" s="40"/>
+    </row>
+    <row r="31" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="11"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="19"/>
+    </row>
+    <row r="33" spans="2:3" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B33" s="38"/>
+      <c r="C33" s="38"/>
+    </row>
+    <row r="72" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="G21:I21"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:I1"/>
     <mergeCell ref="D2:I2"/>
     <mergeCell ref="D3:I3"/>
     <mergeCell ref="D4:I4"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="G30:I30"/>
   </mergeCells>
-  <pageMargins left="0.5" right="1" top="1" bottom="1" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="99" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="90" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>